--- a/frontend/public/data/2025/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2025/fpros/fpros_merged_formatted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B0C4DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7F50"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +94,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7730 +530,7058 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>WR1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Ja'Marr Chase</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>RB1</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Bijan Robinson</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>ATL (5)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>WR2</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CeeDee Lamb</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>WR3</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Justin Jefferson</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RB2</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Jahmyr Gibbs</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>WR4</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Malik Nabers</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>RB3</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Saquon Barkley</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>WR5</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Amon-Ra St. Brown</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>WR6</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Nico Collins</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>WR7</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Puka Nacua</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>LAR (8)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>RB4</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Christian McCaffrey</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>WR8</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Brian Thomas</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>WR9</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Drake London</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>ATL (5)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>RB5</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Ashton Jeanty (R)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>WR10</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>A.J. Brown</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>RB6</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>De'Von Achane</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>TE1</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Brock Bowers</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>WR11</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Ladd McConkey</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>TE2</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Trey McBride</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>ARI (8)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>RB7</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Derrick Henry</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>WR12</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>RB8</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Chase Brown</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>WR13</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Tee Higgins</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>QB1</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Josh Allen</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>RB9</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Bucky Irving</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>QB2</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lamar Jackson</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>WR14</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Garrett Wilson</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>NYJ (9)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>RB10</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Josh Jacobs</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>WR15</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Tyreek Hill</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>RB11</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Jonathan Taylor</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>TE3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>George Kittle</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>WR16</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Davante Adams</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>LAR (8)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>WR17</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Mike Evans</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>QB3</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Jayden Daniels</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>RB12</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Kyren Williams</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>LAR (8)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>WR18</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Marvin Harrison</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>ARI (8)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>QB4</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Jalen Hurts</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>WR19</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Terry McLaurin</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>RB13</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Alvin Kamara</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>RB14</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>James Cook</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>RB15</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Kenneth WalkerI</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Kenneth Walker</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>RB16</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Omarion Hampton (R)</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>WR21</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Courtland Sutton</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>RB17</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Breece Hall</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>NYJ (9)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>WR22</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>DK Metcalf</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>QB5</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Joe Burrow</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>WR23</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>DeVonta Smith</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>WR24</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Tetairoa McMillan (R)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>RB18</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Chuba Hubbard</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>RB19</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>James Conner</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>ARI (8)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>RB20</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>TreVeyon Henderson (R)</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>WR25</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Jaylen Waddle</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>WR26</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Xavier Worthy</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>WR27</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Calvin Ridley</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>WR28</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>George Pickens</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>WR29</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Zay Flowers</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>WR30</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Jameson Williams</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>RB21</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Tony Pollard</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>RB22</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>RJ Harvey (R)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>RB23</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>D'Andre Swift</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>QB6</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Patrick Mahomes</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>TE4</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>T.J. Hockenson</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>WR31</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Chris Olave</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>RB24</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>David Montgomery</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>RB25</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Isiah Pacheco</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>RB26</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Aaron Jones</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>WR32</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Travis Hunter (R)</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>TE5</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Sam LaPorta</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>QB7</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="9" t="n">
         <v>106</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Baker Mayfield</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>WR33</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Rashee Rice (?)</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>WR34</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Jerry Jeudy</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>QB8</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Bo Nix</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>WR35</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Rome Odunze</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>TE6</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Travis Kelce</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>WR36</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Stefon Diggs</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>WR37</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Emeka Egbuka (R)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>WR38</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Ricky Pearsall</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>QB9</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Kyler Murray</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>ARI (8)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>RB27</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Tyrone Tracy</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>RB28</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Jaylen Warren</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>WR39</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Jakobi Meyers</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t>QB10</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="9" t="n">
         <v>107</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Dak Prescott</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>TE7</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="9" t="n">
         <v>122</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>David Njoku</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>TE8</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Evan Engram</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>RB29</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Kaleb Johnson (R)</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>TE9</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Mark Andrews</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>QB11</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Brock Purdy</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>RB30</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Travis Etienne</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>QB12</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Justin Fields</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>NYJ (9)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>WR40</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Khalil Shakir</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>WR41</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Jordan Addison (?)</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>RB31</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Zach Charbonnet</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>WR42</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Deebo Samuel</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>WR43</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Jauan Jennings</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>WR44</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Josh Downs</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>QB13</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="9" t="n">
         <v>111</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Justin Herbert</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>WR45</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Michael Pittman</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>QB14</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Caleb Williams</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>RB32</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Javonte Williams</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>QB15</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Drake Maye</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>RB33</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Jordan Mason</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>TE10</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Tyler Warren (R)</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>WR46</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Matthew Golden (R)</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>QB16</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Jared Goff</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>TE11</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Tucker Kraft</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>WR47</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Cooper Kupp</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>WR48</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="9" t="n">
         <v>125</v>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Chris Godwin (?)</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>TE12</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Jake Ferguson</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>QB17</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Jordan Love</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>WR49</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Jayden Reed</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>QB18</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="9" t="n">
         <v>134</v>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Trevor Lawrence</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>RB34</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Jacory Croskey-Merritt (R)</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>RB35</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>J.K. Dobbins</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>RB36</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>Austin Ekeler</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>QB19</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="9" t="n">
         <v>133</v>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>C.J. Stroud</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>QB20</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>J.J. McCarthy</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>RB37</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Rhamondre Stevenson</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>TE13</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="10" t="n">
         <v>115</v>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Dalton Kincaid</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>WR50</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Darnell Mooney</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>ATL (5)</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>RB38</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Tank Bigsby</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>RB39</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Cam Skattebo (R)</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>WR51</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Keon Coleman</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>TE14</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Dallas Goedert</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t>TE15</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Colston Loveland (R)</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>WR52</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Christian Kirk</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>WR53</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Rashid Shaheed</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>RB40</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="4" t="n">
         <v>166</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>Rachaad White</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="11" t="inlineStr">
         <is>
           <t>QB21</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="9" t="n">
         <v>160</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>WR54</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>Brandon Aiyuk (?)</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>RB41</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="10" t="n">
         <v>126</v>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Braelon Allen</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>NYJ (9)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>QB22</t>
         </is>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Bryce Young</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>RB42</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>Najee Harris</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="11" t="inlineStr">
         <is>
           <t>QB23</t>
         </is>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="9" t="n">
         <v>154</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Michael Penix</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>ATL (5)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>RB43</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Joe Mixon</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>RB44</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Tyjae Spears</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="5" t="inlineStr">
         <is>
           <t>RB45</t>
         </is>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="4" t="n">
         <v>163</v>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Quinshon Judkins (R)</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>WR55</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>146</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Luther Burden (R)</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>CHI (5)</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>RB46</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B139" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C139" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Trey Benson</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>ARI (8)</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>WR56</t>
         </is>
       </c>
-      <c r="B139" t="n">
+      <c r="B140" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C140" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Cedric Tillman</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>TE16</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B141" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C141" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Kyle Pitts (?)</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>ATL (5)</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>TE17</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B142" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C142" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Hunter Henry</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>WR57</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B143" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C143" s="4" t="n">
         <v>118</v>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Rashod Bateman</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>WR58</t>
         </is>
       </c>
-      <c r="B143" t="n">
+      <c r="B144" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C144" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Marvin Mims</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>RB47</t>
         </is>
       </c>
-      <c r="B144" t="n">
+      <c r="B145" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C145" s="10" t="n">
         <v>138</v>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Brian Robinson</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>RB48</t>
         </is>
       </c>
-      <c r="B145" t="n">
+      <c r="B146" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C146" s="7" t="n">
         <v>127</v>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Ray Davis</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t>QB24</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B147" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C147" s="9" t="n">
         <v>178</v>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>Matthew Stafford</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>LAR (8)</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>RB49</t>
         </is>
       </c>
-      <c r="B147" t="n">
+      <c r="B148" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C148" s="4" t="n">
         <v>196</v>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>Jaydon Blue (R)</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>QB25</t>
         </is>
       </c>
-      <c r="B148" t="n">
+      <c r="B149" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C149" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Geno Smith</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>RB50</t>
         </is>
       </c>
-      <c r="B149" t="n">
+      <c r="B150" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C150" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Jerome Ford</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>WR59</t>
         </is>
       </c>
-      <c r="B150" t="n">
+      <c r="B151" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C151" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Jayden Higgins (R)</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>RB51</t>
         </is>
       </c>
-      <c r="B151" t="n">
+      <c r="B152" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C152" s="7" t="n">
         <v>131</v>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Bhayshul Tuten (R)</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>RB52</t>
         </is>
       </c>
-      <c r="B152" t="n">
+      <c r="B153" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C153" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Tyler Allgeier</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>ATL (5)</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>RB53</t>
         </is>
       </c>
-      <c r="B153" t="n">
+      <c r="B154" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C154" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>Dylan Sampson (R)</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>WR60</t>
         </is>
       </c>
-      <c r="B154" t="n">
+      <c r="B155" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C155" s="6" t="n">
         <v>205</v>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Wan'Dale Robinson</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>TE18</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C156" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Zach Ertz</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>RB54</t>
         </is>
       </c>
-      <c r="B156" t="n">
+      <c r="B157" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C157" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Nick Chubb</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>WR61</t>
         </is>
       </c>
-      <c r="B157" t="n">
+      <c r="B158" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C158" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Keenan Allen</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>TE19</t>
         </is>
       </c>
-      <c r="B158" t="n">
+      <c r="B159" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C159" s="4" t="n">
         <v>173</v>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Jonnu Smith</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>WR62</t>
         </is>
       </c>
-      <c r="B159" t="n">
+      <c r="B160" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C160" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Romeo Doubs</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>WR64</t>
         </is>
       </c>
-      <c r="B160" t="n">
+      <c r="B161" s="3" t="n">
         <v>163</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C161" s="4" t="n">
         <v>165</v>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Demario Douglas</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>WR65</t>
         </is>
       </c>
-      <c r="B161" t="n">
+      <c r="B162" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C162" s="6" t="n">
         <v>202</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Adam Thielen</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
         <is>
           <t>QB26</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B163" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C163" s="4" t="n">
         <v>156</v>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Cam Ward (R)</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="11" t="inlineStr">
         <is>
           <t>QB27</t>
         </is>
       </c>
-      <c r="B163" t="n">
+      <c r="B164" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C164" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Sam Darnold</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>WR66</t>
         </is>
       </c>
-      <c r="B164" t="n">
+      <c r="B165" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C165" s="4" t="n">
         <v>164</v>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Kyle Williams (R)</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>RB55</t>
         </is>
       </c>
-      <c r="B165" t="n">
+      <c r="B166" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C166" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Rico Dowdle</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>WR67</t>
         </is>
       </c>
-      <c r="B166" t="n">
+      <c r="B167" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C167" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Tre' Harris (R)</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>TE20</t>
         </is>
       </c>
-      <c r="B167" t="n">
+      <c r="B168" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C168" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Brenton Strange</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>WR68</t>
         </is>
       </c>
-      <c r="B168" t="n">
+      <c r="B169" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C169" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Joshua Palmer</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>WR69</t>
         </is>
       </c>
-      <c r="B169" t="n">
+      <c r="B170" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C170" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Xavier Legette</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>WR70</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B171" s="3" t="n">
         <v>177</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C171" s="4" t="n">
         <v>184</v>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Quentin Johnston</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>LAC (12)</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>WR71</t>
         </is>
       </c>
-      <c r="B171" t="n">
+      <c r="B172" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C172" s="4" t="n">
         <v>183</v>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Jalen Coker</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t>TE21</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B173" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C173" s="10" t="n">
         <v>145</v>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Chig Okonkwo</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>RB56</t>
         </is>
       </c>
-      <c r="B173" t="n">
+      <c r="B174" s="3" t="n">
         <v>184</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C174" s="4" t="n">
         <v>193</v>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Isaac Guerendo</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>SF (14)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>RB57</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B175" s="3" t="n">
         <v>186</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C175" s="4" t="n">
         <v>186</v>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Blake Corum</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>LAR (8)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>RB58</t>
         </is>
       </c>
-      <c r="B175" t="n">
+      <c r="B176" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C176" s="4" t="n">
         <v>187</v>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Ollie Gordon (R)</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>RB59</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B177" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C177" s="6" t="n">
         <v>223</v>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Woody Marks (R)</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>RB60</t>
         </is>
       </c>
-      <c r="B177" t="n">
+      <c r="B178" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C178" s="4" t="n">
         <v>170</v>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Roschon Johnson</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>WR72</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B179" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C179" s="4" t="n">
         <v>197</v>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>DeAndre Hopkins</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>RB61</t>
         </is>
       </c>
-      <c r="B179" t="n">
+      <c r="B180" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C180" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Jaylen Wright</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>TE22</t>
         </is>
       </c>
-      <c r="B180" t="n">
+      <c r="B181" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C181" s="4" t="n">
         <v>174</v>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Cade Otton</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="11" t="inlineStr">
         <is>
           <t>QB28</t>
         </is>
       </c>
-      <c r="B181" t="n">
+      <c r="B182" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C182" s="4" t="n">
         <v>181</v>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Aaron Rodgers</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>TE23</t>
         </is>
       </c>
-      <c r="B182" t="n">
+      <c r="B183" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C183" s="4" t="n">
         <v>209</v>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>Mike Gesicki</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="8" t="inlineStr">
         <is>
           <t>TE24</t>
         </is>
       </c>
-      <c r="B183" t="n">
+      <c r="B184" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C184" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Pat Freiermuth</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t>TE25</t>
         </is>
       </c>
-      <c r="B184" t="n">
+      <c r="B185" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C185" s="10" t="n">
         <v>162</v>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>Mason Taylor (R)</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>NYJ (9)</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
         <is>
           <t>TE26</t>
         </is>
       </c>
-      <c r="B185" t="n">
+      <c r="B186" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="C185" t="n">
+      <c r="C186" s="10" t="n">
         <v>172</v>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>Isaiah Likely</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>WR73</t>
         </is>
       </c>
-      <c r="B186" t="n">
+      <c r="B187" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C187" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Michael Wilson</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>ARI (8)</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>WR74</t>
         </is>
       </c>
-      <c r="B187" t="n">
+      <c r="B188" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C188" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>Alec Pierce</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
         <is>
           <t>RB62</t>
         </is>
       </c>
-      <c r="B188" t="n">
+      <c r="B189" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C189" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>Will Shipley</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>PHI (9)</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>WR75</t>
         </is>
       </c>
-      <c r="B189" t="n">
+      <c r="B190" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C190" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>Jack Bech (R)</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>WR76</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B191" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C191" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>Adonai Mitchell</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
         <is>
           <t>RB63</t>
         </is>
       </c>
-      <c r="B191" t="n">
+      <c r="B192" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C192" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>Justice Hill</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>WR77</t>
         </is>
       </c>
-      <c r="B192" t="n">
+      <c r="B193" s="3" t="n">
         <v>219</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C193" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>Pat Bryant (R)</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>WR78</t>
         </is>
       </c>
-      <c r="B193" t="n">
+      <c r="B194" s="3" t="n">
         <v>220</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C194" s="10" t="n">
         <v>143</v>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>Darius Slayton</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>WR79</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B195" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C195" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>Elic Ayomanor (R)</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="11" t="inlineStr">
         <is>
           <t>QB29</t>
         </is>
       </c>
-      <c r="B195" t="n">
+      <c r="B196" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C196" s="10" t="n">
         <v>179</v>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>Daniel Jones</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
         <is>
           <t>RB64</t>
         </is>
       </c>
-      <c r="B196" t="n">
+      <c r="B197" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C197" s="10" t="n">
         <v>169</v>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>DJ Giddens (R)</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>WR80</t>
         </is>
       </c>
-      <c r="B197" t="n">
+      <c r="B198" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C198" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>Andrei Iosivas</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
         <is>
           <t>RB65</t>
         </is>
       </c>
-      <c r="B198" t="n">
+      <c r="B199" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C199" s="10" t="n">
         <v>189</v>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Chris Rodriguez</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>WAS (12)</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
         <is>
           <t>RB66</t>
         </is>
       </c>
-      <c r="B199" t="n">
+      <c r="B200" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C200" s="4" t="n">
         <v>225</v>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>Kareem Hunt</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>WR81</t>
         </is>
       </c>
-      <c r="B200" t="n">
+      <c r="B201" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C201" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Jaylin Noel (R)</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
         <is>
           <t>RB67</t>
         </is>
       </c>
-      <c r="B201" t="n">
+      <c r="B202" s="3" t="n">
         <v>229</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C202" s="10" t="n">
         <v>191</v>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>Kendre Miller</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
         <is>
           <t>RB68</t>
         </is>
       </c>
-      <c r="B202" t="n">
+      <c r="B203" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C203" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>Kyle Monangai (R)</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>WR82</t>
         </is>
       </c>
-      <c r="B203" t="n">
+      <c r="B204" s="3" t="n">
         <v>231</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C204" s="4" t="n">
         <v>249</v>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Jalen McMillan</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
         <is>
           <t>TE27</t>
         </is>
       </c>
-      <c r="B204" t="n">
+      <c r="B205" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C205" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>Dalton Schultz</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="11" t="inlineStr">
         <is>
           <t>QB30</t>
         </is>
       </c>
-      <c r="B205" t="n">
+      <c r="B206" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C206" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>Russell Wilson</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
         <is>
           <t>RB69</t>
         </is>
       </c>
-      <c r="B206" t="n">
+      <c r="B207" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C207" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>MarShawn Lloyd</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>WR83</t>
         </is>
       </c>
-      <c r="B207" t="n">
+      <c r="B208" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C208" s="4" t="n">
         <v>236</v>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Calvin AustinI</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Calvin Austin</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>WR84</t>
         </is>
       </c>
-      <c r="B208" t="n">
+      <c r="B209" s="3" t="n">
         <v>236</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C209" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>Tyler Lockett</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>TEN (10)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
         <is>
           <t>RB70</t>
         </is>
       </c>
-      <c r="B209" t="n">
+      <c r="B210" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C210" s="10" t="n">
         <v>190</v>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>Keaton Mitchell</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>BAL (7)</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>WR85</t>
         </is>
       </c>
-      <c r="B210" t="n">
+      <c r="B211" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C211" s="4" t="n">
         <v>250</v>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>Dontayvion Wicks</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>GB (5)</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
         <is>
           <t>TE28</t>
         </is>
       </c>
-      <c r="B211" t="n">
+      <c r="B212" s="3" t="n">
         <v>241</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C212" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>Ja'Tavion Sanders</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>TE29</t>
         </is>
       </c>
-      <c r="B212" t="n">
+      <c r="B213" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C213" s="4" t="n">
         <v>252</v>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t>Elijah Arroyo (R)</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
         <is>
           <t>RB71</t>
         </is>
       </c>
-      <c r="B213" t="n">
+      <c r="B214" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C214" s="10" t="n">
         <v>157</v>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>Dameon Pierce</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>HOU (6)</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>WR86</t>
         </is>
       </c>
-      <c r="B214" t="n">
+      <c r="B215" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C214" t="n">
+      <c r="C215" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>Dyami Brown</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>JAC (8)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
         <is>
           <t>TE30</t>
         </is>
       </c>
-      <c r="B215" t="n">
+      <c r="B216" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C216" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t>Juwan Johnson</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F216" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
         <is>
           <t>RB72</t>
         </is>
       </c>
-      <c r="B216" t="n">
+      <c r="B217" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C217" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t>Brashard Smith (R)</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
         <is>
           <t>RB73</t>
         </is>
       </c>
-      <c r="B217" t="n">
+      <c r="B218" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C218" s="10" t="n">
         <v>192</v>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>Tahj Brooks (R)</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>CIN (10)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>WR87</t>
         </is>
       </c>
-      <c r="B218" t="n">
+      <c r="B219" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C219" s="10" t="n">
         <v>199</v>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>Dont'e Thornton (R)</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>WR88</t>
         </is>
       </c>
-      <c r="B219" t="n">
+      <c r="B220" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C220" s="4" t="n">
         <v>263</v>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t>Jalen Royals (R)</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>WR89</t>
         </is>
       </c>
-      <c r="B220" t="n">
+      <c r="B221" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C221" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>Tory Horton (R)</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>SEA (8)</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
         <is>
           <t>RB74</t>
         </is>
       </c>
-      <c r="B221" t="n">
+      <c r="B222" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C222" s="10" t="n">
         <v>195</v>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>Miles Sanders</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>WR90</t>
         </is>
       </c>
-      <c r="B222" t="n">
+      <c r="B223" s="3" t="n">
         <v>253</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C223" s="4" t="n">
         <v>234</v>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t>Devaughn Vele</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>WR91</t>
         </is>
       </c>
-      <c r="B223" t="n">
+      <c r="B224" s="3" t="n">
         <v>254</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C224" s="4" t="n">
         <v>237</v>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>Roman Wilson</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>PIT (5)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
         <is>
           <t>RB75</t>
         </is>
       </c>
-      <c r="B224" t="n">
+      <c r="B225" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C225" s="4" t="n">
         <v>275</v>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D225" s="3" t="inlineStr">
         <is>
           <t>Jaleel McLaughlin</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>DEN (12)</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="inlineStr">
         <is>
           <t>TE31</t>
         </is>
       </c>
-      <c r="B225" t="n">
+      <c r="B226" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C226" s="4" t="n">
         <v>256</v>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D226" s="3" t="inlineStr">
         <is>
           <t>Cole Kmet</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>CHI (5)</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F226" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>RB76</t>
         </is>
       </c>
-      <c r="B226" t="n">
+      <c r="B227" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C227" s="4" t="n">
         <v>221</v>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D227" s="3" t="inlineStr">
         <is>
           <t>Jarquez Hunter (R)</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E227" s="3" t="inlineStr">
         <is>
           <t>LAR (8)</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="11" t="inlineStr">
         <is>
           <t>QB31</t>
         </is>
       </c>
-      <c r="B227" t="n">
+      <c r="B228" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C228" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D228" s="3" t="inlineStr">
         <is>
           <t>Anthony Richardson</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>IND (11)</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F228" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="11" t="inlineStr">
         <is>
           <t>QB32</t>
         </is>
       </c>
-      <c r="B228" t="n">
+      <c r="B229" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C229" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D229" s="3" t="inlineStr">
         <is>
           <t>Joe Flacco</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F229" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>WR92</t>
         </is>
       </c>
-      <c r="B229" t="n">
+      <c r="B230" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C230" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D230" s="3" t="inlineStr">
         <is>
           <t>Isaac TeSlaa (R)</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>DET (8)</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>WR93</t>
         </is>
       </c>
-      <c r="B230" t="n">
+      <c r="B231" s="3" t="n">
         <v>263</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C231" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D231" s="3" t="inlineStr">
         <is>
           <t>Malik Washington</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E231" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
         <is>
           <t>RB77</t>
         </is>
       </c>
-      <c r="B231" t="n">
+      <c r="B232" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="C231" t="n">
+      <c r="C232" s="4" t="n">
         <v>276</v>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D232" s="3" t="inlineStr">
         <is>
           <t>Devin Neal (R)</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E232" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
         <is>
           <t>TE32</t>
         </is>
       </c>
-      <c r="B232" t="n">
+      <c r="B233" s="3" t="n">
         <v>265</v>
       </c>
-      <c r="C232" t="n">
+      <c r="C233" s="10" t="n">
         <v>194</v>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t>Harold Fannin (R)</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>CLE (9)</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F233" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
         <is>
           <t>RB78</t>
         </is>
       </c>
-      <c r="B233" t="n">
+      <c r="B234" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="C233" t="n">
+      <c r="C234" s="4" t="n">
         <v>224</v>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>Raheem Mostert</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>WR94</t>
         </is>
       </c>
-      <c r="B234" t="n">
+      <c r="B235" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="C234" t="n">
+      <c r="C235" s="4" t="n">
         <v>264</v>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D235" s="3" t="inlineStr">
         <is>
           <t>Brandin Cooks</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E235" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>WR95</t>
         </is>
       </c>
-      <c r="B235" t="n">
+      <c r="B236" s="3" t="n">
         <v>268</v>
       </c>
-      <c r="C235" t="n">
+      <c r="C236" s="4" t="n">
         <v>261</v>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D236" s="3" t="inlineStr">
         <is>
           <t>Jalen Tolbert</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>DAL (10)</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
         <is>
           <t>TE33</t>
         </is>
       </c>
-      <c r="B236" t="n">
+      <c r="B237" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C236" t="n">
+      <c r="C237" s="10" t="n">
         <v>168</v>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D237" s="3" t="inlineStr">
         <is>
           <t>Theo Johnson</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F237" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
         <is>
           <t>RB79</t>
         </is>
       </c>
-      <c r="B237" t="n">
+      <c r="B238" s="3" t="n">
         <v>270</v>
       </c>
-      <c r="C237" t="n">
+      <c r="C238" s="4" t="n">
         <v>229</v>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D238" s="3" t="inlineStr">
         <is>
           <t>Sean Tucker</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
         <is>
           <t>TB (9)</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>WR97</t>
         </is>
       </c>
-      <c r="B238" t="n">
+      <c r="B239" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C238" t="n">
+      <c r="C239" s="4" t="n">
         <v>243</v>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D239" s="3" t="inlineStr">
         <is>
           <t>Kayshon Boutte</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>NE (14)</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
         <is>
           <t>RB81</t>
         </is>
       </c>
-      <c r="B239" t="n">
+      <c r="B240" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="C239" t="n">
+      <c r="C240" s="4" t="n">
         <v>246</v>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D240" s="3" t="inlineStr">
         <is>
           <t>Trevor Etienne (R)</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>CAR (14)</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
         <is>
           <t>TE34</t>
         </is>
       </c>
-      <c r="B240" t="n">
+      <c r="B241" s="3" t="n">
         <v>276</v>
       </c>
-      <c r="C240" t="n">
+      <c r="C241" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D241" s="3" t="inlineStr">
         <is>
           <t>Noah Gray</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E241" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="F241" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>WR98</t>
         </is>
       </c>
-      <c r="B241" t="n">
+      <c r="B242" s="3" t="n">
         <v>277</v>
       </c>
-      <c r="C241" t="n">
+      <c r="C242" s="4" t="n">
         <v>269</v>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D242" s="3" t="inlineStr">
         <is>
           <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
         <is>
           <t>RB83</t>
         </is>
       </c>
-      <c r="B242" t="n">
+      <c r="B243" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="C242" t="n">
+      <c r="C243" s="4" t="n">
         <v>274</v>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D243" s="3" t="inlineStr">
         <is>
           <t>Elijah Mitchell</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>KC (10)</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>WR99</t>
         </is>
       </c>
-      <c r="B243" t="n">
+      <c r="B244" s="3" t="n">
         <v>282</v>
       </c>
-      <c r="C243" t="n">
+      <c r="C244" s="4" t="n">
         <v>279</v>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D244" s="3" t="inlineStr">
         <is>
           <t>Amari Cooper (?)</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E244" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>WR100</t>
         </is>
       </c>
-      <c r="B244" t="n">
+      <c r="B245" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="C244" t="n">
+      <c r="C245" s="10" t="n">
         <v>198</v>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D245" s="3" t="inlineStr">
         <is>
           <t>Tre Tucker</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E245" s="3" t="inlineStr">
         <is>
           <t>LV (8)</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="11" t="inlineStr">
         <is>
           <t>QB33</t>
         </is>
       </c>
-      <c r="B245" t="n">
+      <c r="B246" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="C245" t="n">
+      <c r="C246" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D246" s="3" t="inlineStr">
         <is>
           <t>Jaxson Dart (R)</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
+      <c r="F246" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="11" t="inlineStr">
         <is>
           <t>QB34</t>
         </is>
       </c>
-      <c r="B246" t="n">
+      <c r="B247" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="C246" t="n">
+      <c r="C247" s="4" t="n">
         <v>232</v>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D247" s="3" t="inlineStr">
         <is>
           <t>Tyler Shough (R)</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E247" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F247" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="8" t="inlineStr">
         <is>
           <t>TE35</t>
         </is>
       </c>
-      <c r="B247" t="n">
+      <c r="B248" s="3" t="n">
         <v>286</v>
       </c>
-      <c r="C247" t="n">
+      <c r="C248" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D248" s="3" t="inlineStr">
         <is>
           <t>Darren Waller</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E248" s="3" t="inlineStr">
         <is>
           <t>MIA (12)</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
+      <c r="F248" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
         <is>
           <t>RB85</t>
         </is>
       </c>
-      <c r="B248" t="n">
+      <c r="B249" s="3" t="n">
         <v>287</v>
       </c>
-      <c r="C248" t="n">
+      <c r="C249" s="4" t="n">
         <v>227</v>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D249" s="3" t="inlineStr">
         <is>
           <t>Devin Singletary</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>NYG (14)</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="11" t="inlineStr">
         <is>
           <t>QB35</t>
         </is>
       </c>
-      <c r="B249" t="n">
+      <c r="B250" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="C249" t="n">
+      <c r="C250" s="4" t="n">
         <v>231</v>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D250" s="3" t="inlineStr">
         <is>
           <t>Spencer Rattler</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E250" s="3" t="inlineStr">
         <is>
           <t>NO (11)</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="F250" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>WR101</t>
         </is>
       </c>
-      <c r="B250" t="n">
+      <c r="B251" s="3" t="n">
         <v>289</v>
       </c>
-      <c r="C250" t="n">
+      <c r="C251" s="4" t="n">
         <v>278</v>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D251" s="3" t="inlineStr">
         <is>
           <t>Diontae Johnson</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E251" s="3" t="inlineStr">
         <is>
           <t>FA (-)</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>WR102</t>
         </is>
       </c>
-      <c r="B251" t="n">
+      <c r="B252" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="C251" t="n">
+      <c r="C252" s="4" t="n">
         <v>235</v>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D252" s="3" t="inlineStr">
         <is>
           <t>Jalen Nailor</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E252" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
         <is>
           <t>RB86</t>
         </is>
       </c>
-      <c r="B252" t="n">
+      <c r="B253" s="3" t="n">
         <v>291</v>
       </c>
-      <c r="C252" t="n">
+      <c r="C253" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D253" s="3" t="inlineStr">
         <is>
           <t>Isaiah Davis</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E253" s="3" t="inlineStr">
         <is>
           <t>NYJ (9)</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
-      <c r="B253" t="n">
-        <v>302</v>
-      </c>
-      <c r="C253" t="n">
-        <v>251</v>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Terrance Ferguson (R)</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>LAR (8)</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>WR106</t>
-        </is>
-      </c>
-      <c r="B254" t="n">
-        <v>303</v>
-      </c>
-      <c r="C254" t="n">
-        <v>200</v>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Troy Franklin</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>DEN (12)</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>WR107</t>
-        </is>
-      </c>
-      <c r="B255" t="n">
-        <v>306</v>
-      </c>
-      <c r="C255" t="n">
-        <v>267</v>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>GB (5)</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>WR108</t>
-        </is>
-      </c>
-      <c r="B256" t="n">
-        <v>307</v>
-      </c>
-      <c r="C256" t="n">
-        <v>233</v>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Ray-Ray McCloudI</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>ATL (5)</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>TE38</t>
-        </is>
-      </c>
-      <c r="B257" t="n">
-        <v>309</v>
-      </c>
-      <c r="C257" t="n">
-        <v>253</v>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Noah Fant</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>CIN (10)</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>WR110</t>
-        </is>
-      </c>
-      <c r="B258" t="n">
-        <v>311</v>
-      </c>
-      <c r="C258" t="n">
-        <v>244</v>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Tutu Atwell</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>LAR (8)</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>TE39</t>
-        </is>
-      </c>
-      <c r="B259" t="n">
-        <v>314</v>
-      </c>
-      <c r="C259" t="n">
-        <v>254</v>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Tyler Higbee</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>LAR (8)</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>RB95</t>
-        </is>
-      </c>
-      <c r="B260" t="n">
-        <v>320</v>
-      </c>
-      <c r="C260" t="n">
-        <v>270</v>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Phil Mafah (R)</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>DAL (10)</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>TE40</t>
-        </is>
-      </c>
-      <c r="B261" t="n">
-        <v>322</v>
-      </c>
-      <c r="C261" t="n">
-        <v>271</v>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Oronde Gadsden (R)</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>LAC (12)</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>WR114</t>
-        </is>
-      </c>
-      <c r="B262" t="n">
-        <v>326</v>
-      </c>
-      <c r="C262" t="n">
-        <v>238</v>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Josh Reynolds</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>NYJ (9)</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>TE41</t>
-        </is>
-      </c>
-      <c r="B263" t="n">
-        <v>329</v>
-      </c>
-      <c r="C263" t="n">
-        <v>272</v>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Ben Sinnott</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>WAS (12)</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>WR115</t>
-        </is>
-      </c>
-      <c r="B264" t="n">
-        <v>330</v>
-      </c>
-      <c r="C264" t="n">
-        <v>260</v>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Noah Brown</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>WAS (12)</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>WR116</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>331</v>
-      </c>
-      <c r="C265" t="n">
-        <v>248</v>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>KaVontae Turpin</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>DAL (10)</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>TE43</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>333</v>
-      </c>
-      <c r="C266" t="n">
-        <v>273</v>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Will Dissly</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>LAC (12)</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>QB37</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>338</v>
-      </c>
-      <c r="C267" t="n">
-        <v>259</v>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Jalen Milroe (R)</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>SEA (8)</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>WR118</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>340</v>
-      </c>
-      <c r="C268" t="n">
-        <v>219</v>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>KeAndre Lambert-Smith (R)</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>LAC (12)</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>WR123</t>
-        </is>
-      </c>
-      <c r="B269" t="n">
-        <v>349</v>
-      </c>
-      <c r="C269" t="n">
-        <v>268</v>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Tai Felton (R)</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>WR124</t>
-        </is>
-      </c>
-      <c r="B270" t="n">
-        <v>351</v>
-      </c>
-      <c r="C270" t="n">
-        <v>239</v>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Olamide Zaccheaus</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>CHI (5)</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>TE46</t>
-        </is>
-      </c>
-      <c r="B271" t="n">
-        <v>352</v>
-      </c>
-      <c r="C271" t="n">
-        <v>212</v>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>AJ Barner</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>SEA (8)</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>QB38</t>
-        </is>
-      </c>
-      <c r="B272" t="n">
-        <v>354</v>
-      </c>
-      <c r="C272" t="n">
-        <v>258</v>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Kirk Cousins (?)</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>ATL (5)</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>WR125</t>
-        </is>
-      </c>
-      <c r="B273" t="n">
-        <v>355</v>
-      </c>
-      <c r="C273" t="n">
-        <v>262</v>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>Marquez Valdes-Scantling</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>SF (14)</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>WR126</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>357</v>
-      </c>
-      <c r="C274" t="n">
-        <v>265</v>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Allen Lazard</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>NYJ (9)</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>WR128</t>
-        </is>
-      </c>
-      <c r="B275" t="n">
-        <v>361</v>
-      </c>
-      <c r="C275" t="n">
-        <v>277</v>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Chimere Dike (R)</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>TEN (10)</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>WR132</t>
-        </is>
-      </c>
-      <c r="B276" t="n">
-        <v>374</v>
-      </c>
-      <c r="C276" t="n">
-        <v>266</v>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Jahan Dotson</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>PHI (9)</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>QB42</t>
-        </is>
-      </c>
-      <c r="B277" t="n">
-        <v>393</v>
-      </c>
-      <c r="C277" t="n">
-        <v>257</v>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Kenny Pickett</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>LV (8)</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>QB</t>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
     </row>
